--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N152_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N152_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.04351623834496</v>
+        <v>3.419571388731056</v>
       </c>
       <c r="D2" t="n">
-        <v>23.81524395925691</v>
+        <v>3.869977143379248</v>
       </c>
       <c r="E2" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F2" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.48349296816272</v>
+        <v>10.64106760732644</v>
       </c>
       <c r="D3" t="n">
-        <v>65.75811550253849</v>
+        <v>10.6856937691625</v>
       </c>
       <c r="E3" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F3" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.60152725486279</v>
+        <v>4.160248178915204</v>
       </c>
       <c r="D4" t="n">
-        <v>27.52949078962873</v>
+        <v>4.47354225331467</v>
       </c>
       <c r="E4" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F4" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.35444698240174</v>
+        <v>4.282597634640283</v>
       </c>
       <c r="D5" t="n">
-        <v>26.25428621179631</v>
+        <v>4.2663215094169</v>
       </c>
       <c r="E5" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F5" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.11378329519486</v>
+        <v>9.768489785469164</v>
       </c>
       <c r="D6" t="n">
-        <v>60.36585430500276</v>
+        <v>9.809451324562948</v>
       </c>
       <c r="E6" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F6" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.80570695275627</v>
+        <v>3.380927379822893</v>
       </c>
       <c r="D7" t="n">
-        <v>21.08659355125017</v>
+        <v>3.426571452078154</v>
       </c>
       <c r="E7" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F7" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.863049156215768</v>
+        <v>1.277745487885062</v>
       </c>
       <c r="D8" t="n">
-        <v>8.082166333617105</v>
+        <v>1.31335202921278</v>
       </c>
       <c r="E8" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F8" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.02624677623443</v>
+        <v>5.529265101138095</v>
       </c>
       <c r="D9" t="n">
-        <v>34.03712219878911</v>
+        <v>5.531032357303231</v>
       </c>
       <c r="E9" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F9" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.68631418942856</v>
+        <v>5.474026055782142</v>
       </c>
       <c r="D10" t="n">
-        <v>32.70753621850599</v>
+        <v>5.314974635507223</v>
       </c>
       <c r="E10" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F10" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.50167455714412</v>
+        <v>4.14402211553592</v>
       </c>
       <c r="D11" t="n">
-        <v>24.51538423558549</v>
+        <v>3.983749938282642</v>
       </c>
       <c r="E11" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F11" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.05008012301053</v>
+        <v>2.933138019989211</v>
       </c>
       <c r="D12" t="n">
-        <v>17.18575695070044</v>
+        <v>2.792685504488822</v>
       </c>
       <c r="E12" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F12" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>33.84699091039369</v>
+        <v>5.500136022938976</v>
       </c>
       <c r="D13" t="n">
-        <v>34.00977013571165</v>
+        <v>5.526587647053145</v>
       </c>
       <c r="E13" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F13" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.29937770414593</v>
+        <v>2.486148876923714</v>
       </c>
       <c r="D14" t="n">
-        <v>17.47363187840735</v>
+        <v>2.839465180241195</v>
       </c>
       <c r="E14" t="n">
-        <v>15.87615628036917</v>
+        <v>2.57987539555999</v>
       </c>
       <c r="F14" t="n">
-        <v>15.7119360202168</v>
+        <v>2.55318960328523</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
